--- a/data/triage_results.xlsx
+++ b/data/triage_results.xlsx
@@ -436,7 +436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -527,7 +527,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>76.67%</t>
+          <t>96.67%</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -746,25 +746,25 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -789,10 +789,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
